--- a/tools/xlsform_samples/DEMO.xlsx
+++ b/tools/xlsform_samples/DEMO.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which of the following devices do you use regularly? (Select all that apply — choose between 1 and 4)</t>
+          <t>Which of the following devices do you use regularly? (Select all that apply -- choose between 1 and 4)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>How many years ago did you complete this degree? (This item appears only when a non-Other field is selected — demonstrating item-level visibility.)</t>
+          <t>How many years ago did you complete this degree? (This item appears only when a non-Other field is selected -- demonstrating item-level visibility.)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Please briefly describe your field. (This item appears only when 'Other' is selected — demonstrating item-level conditional display.)</t>
+          <t>Please briefly describe your field. (This item appears only when 'Other' is selected -- demonstrating item-level conditional display.)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Overall, how would you rate your experience completing {study_name}? (7-point scale — demonstrating per-item Likert override and {study_name} text substitution)</t>
+          <t>Overall, how would you rate your experience completing {study_name}? (7-point scale -- demonstrating per-item Likert override and {study_name} text substitution)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>

--- a/tools/xlsform_samples/DEMO.xlsx
+++ b/tools/xlsform_samples/DEMO.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1838,28 +1838,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEMO_scoring</t>
+          <t>DEMO_attitudes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>attitudes (mean_coded) - Mean of attitude items after reverse-scoring att3 and att5. Branch items (context_general_q* or context_workplace_q*) contribute only one pair depending on parameter; NA respo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>(${context_general_q1} + ${context_general_q2} + ${context_workplace_q1} + ${context_workplace_q2} + (6 - ${att3}) + (6 - ${att5}) + ${att1} + ${att2} + ${att4}) div 9</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEMO_attitudes</t>
+          <t>DEMO_wellbeing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>attitudes (mean_coded) - Mean of attitude items after reverse-scoring att3 and att5. Branch items (context_general_q* or context_workplace_q*) contribute only one pair depending on parameter; NA respo</t>
+          <t>wellbeing (mean_coded) - Mean of 3 VAS items. Range 0-100. Higher = greater subjective well-being. Transformed: divided by 10 to produce 0-10 scale.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1886,7 +1886,7 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(${context_general_q1} + ${context_general_q2} + ${context_workplace_q1} + ${context_workplace_q2} + (6 - ${att3}) + (6 - ${att5}) + ${att1} + ${att2} + ${att4}) div 9</t>
+          <t>((${wb1} + ${wb2} + ${wb3}) div 3) div 10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -1894,58 +1894,6 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>DEMO_wellbeing</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>wellbeing (mean_coded) - Mean of 3 VAS items. Range 0-100. Higher = greater subjective well-being. Transformed: divided by 10 to produce 0-10 scale.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>((${wb1} + ${wb2} + ${wb3}) div 3) div 10</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>DEMO_scoring</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/DEMO.xlsx
+++ b/tools/xlsform_samples/DEMO.xlsx
@@ -2550,7 +2550,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
